--- a/auto OMS Python/engines/shopee/basic_chihuy2309.xlsx
+++ b/auto OMS Python/engines/shopee/basic_chihuy2309.xlsx
@@ -2578,65 +2578,6 @@
 Đừng bỏ lỡ phụ kiện quan trọng này! Đặt mua Bộ Nối Đầu Vòi Lọc Nước ngay hôm nay!</t>
   </si>
   <si>
-    <t>11277881543</t>
-  </si>
-  <si>
-    <t>Lõi Lọc Nước Thay Thế K195 (Combo 2) – Chống Bẩn, Lọc Cặn Lâu Dài, Dễ Dàng Lắp Đặt</t>
-  </si>
-  <si>
-    <t>⏱️ Lõi Lọc Thay Thế K195 – Bảo Vệ Chất Lượng Nước Liên Tục
-Việc thay lõi lọc định kỳ là yếu tố then chốt để đảm bảo nguồn nước sinh hoạt luôn sạch. Với COMBO 2 Lõi Lọc K195, bạn sẽ luôn có sẵn lõi mới để thay ngay khi lõi cũ bị bẩn.
-✅ Khi nào cần thay lõi lọc?
-Thời gian: Tùy thuộc vào chất lượng nguồn nước tại khu vực bạn sinh sống.
-Dấu hiệu nhận biết: Khi lõi lọc chuyển sang màu ố vàng hoặc màu nâu sậm (như hình minh họa) là lúc bạn phải thay ngay để đảm bảo hiệu suất lọc.
-Lõi lọc được thiết kế chắc chắn, dễ dàng tháo lắp. Đầu tư ngay Combo 2 Lõi Lọc K195 để bảo vệ thiết bị lọc nước của bạn và duy trì chất lượng nước tốt nhất!</t>
-  </si>
-  <si>
-    <t>16381031412</t>
-  </si>
-  <si>
-    <t>Bộ Lọc Nước Cho Vòi Sen, Lavabo, Máy Giặt – Dễ Lắp Đặt, Lọc Sạch Bùn Cát K195</t>
-  </si>
-  <si>
-    <t>Bộ Lọc Nước Đầu Nguồn Vòi Hoa Sen,Bồn Rửa Chén,Lavabo,Máy Giặt Lọc Siêu Sạch Các Tạp Chất Dễ Dàng Lắp Đặt Không Ảnh Hưởng Đến Áp Lực Nước K195
-Ưu Điểm Lớn Nhất của sản phẩm là: 
-- Lọc Cặn Siêu Nhỏ (0.5 - 5micron) có khả năng lọc tất cả các tạp chất như bùn, cát mịn, giun, rong rêu, trứng côn trùng Và Không ảnh hưởng đến áp lực nước
-- Lọc nước sạch và trong
-- An toàn khi sử dụng với nước nóng
-- Dễ dàng lắp đặt
-- Thích hợp cho các loại vòi và vòi hoa sen (Ren kích thước tiêu chuẩn 21)
-- Lõi lọc bông PP có thể thay thế được. Thời gian dùng từ 1 - 3 tháng tùy thuộc vào tình trạng sạch dơ của nước.
-   Thông Tin Sản Phẩm
-  - Phân Loại 1 : 
- - Tên Sản Phẩm : Bộ Lọc Nước Đầu Nguồn
- - Chất Liệu : Nhựa PP Cao Cấp An Toàn
- - Kích Thước : 15,9cm x 7,5 cm
- - Bộ Sản Phẩm Gồm : Bộ Lọc Nước + Kèm Lõi Lọc
- - Hướng Dẫn Sử Dụng : Lắp Đặt Phù hợp với dây sen, dây xịt, dây cấp nước, van khóa nước có ren 21mm (4 phân)
- - Xuất Xứ : Trung Quốc
- - Sản Phẩm Được Nhập Và Phân Phối Bởi Kho Gia Dụng Huy Vân
- - .
-Phân Loại 2 : 
- - Tên Sản Phẩm : Lõi Lọc Thay Thế
- - Chất Liệu : Bông PP Cao Cấp 5 Micron Lọc Sạch Các Tạp Chất Siêu Nhỏ
- - Lõi: màn lọc PP 0.5 - 5micron
- - Kích Thước : 11,8cm x 4,7 cm
- - Hướng Dẫn Sử Dụng : Lắp Đặt Thay Thế Lõi Lọc Cho Bộ Lọc Đầu Nguồn
- - Xuất Xứ : Trung Quốc
- ★ Lưu ý: 
-  - do chênh lệch ánh sáng và màn hình, màu sắc của sản phẩm có thể hơi khác so với hình ảnh.
-  - Vui Lòng Cho Phép Sai Số 1-2cm do đo lường thủ công
- Dịch vụ tốt nhất:
- ★ Cam Kết Sản Phẩm Và Chất Lượng Như Hình Và Video Shop Đăng,Tuyệt Đối Không Bán Hàng Kém Chất Lượng ảnh hưởng đến UY TÍN Của Shop
- ★ Ship Hoả Tốc Trong Vòng 2H Kể Từ Khi Khách Đặt Hàng (Xác Nhận Đơn Đến 19-20H Hàng Ngày)
- ★ Cam Kết Giao Đơn Hàng Cho Đơn Vị Vận Chuyển Trong Vòng 24H Kể Từ Khi Qúi Khách Đặt Hàng
- ★ Hàng Hoá Luôn Có Sẵn Khách Đặt Được Là Còn Hàng ( Nếu Hết Hàng Shop Sẽ Gọi Điện Liên Hệ Khách Trước Khi Giao)
- ★ Luôn Kiểm Tra Kỹ Hàng Hoá Trước Khi Giao Cho Khách.
- ★ Bảo vệ khách hàng : Khi Nhận Được Sản Phẩm Bị Thiếu Hoặc Lỗi Do Phía Vận Chuyển Qúi Khách Vui Lòng Liên Hệ Lại Shop Để Shop xử lý Vấn Đề Ngay ạ
- ★ Qúi Khách có thể thấy rằng ai đó bán với giá thấp hơn chúng tôi nhưng họ không thể đảm bảo chất lượng và dịch vụ như chúng tôi, cảm ơn bạn!
-#bolocvoisen #bolocvoihoasen #bolocsentam #bolocnuocvoisen #bolocnuocvoihoasen #bolocnuocsentam</t>
-  </si>
-  <si>
     <t>13040839585</t>
   </si>
   <si>
@@ -2683,6 +2624,65 @@
 #khungluoilocrac
 #tuilocrac
 #luoilocrac #lưới_lọc_rác #lưới_lọc #lưới #lọc #rác #lọc_thức_ăn #lọc_cặn_bẩn #lưới_lọc_cặn_bẩn #luoiloccanthucan #cặn_thức_ăn #lưới_lọc_cặn_thức_ăn #lọc_cặn_thức_ăn #nấu_ăn #bếp #dọn_bếp #tắc_cống #tắc_đường_ống #thongcong #vesinhnhacua  #chất_lượng_cao</t>
+  </si>
+  <si>
+    <t>11277881543</t>
+  </si>
+  <si>
+    <t>Lõi Lọc Nước Thay Thế K195 (Combo 2) – Chống Bẩn, Lọc Cặn Lâu Dài, Dễ Dàng Lắp Đặt</t>
+  </si>
+  <si>
+    <t>⏱️ Lõi Lọc Thay Thế K195 – Bảo Vệ Chất Lượng Nước Liên Tục
+Việc thay lõi lọc định kỳ là yếu tố then chốt để đảm bảo nguồn nước sinh hoạt luôn sạch. Với COMBO 2 Lõi Lọc K195, bạn sẽ luôn có sẵn lõi mới để thay ngay khi lõi cũ bị bẩn.
+✅ Khi nào cần thay lõi lọc?
+Thời gian: Tùy thuộc vào chất lượng nguồn nước tại khu vực bạn sinh sống.
+Dấu hiệu nhận biết: Khi lõi lọc chuyển sang màu ố vàng hoặc màu nâu sậm (như hình minh họa) là lúc bạn phải thay ngay để đảm bảo hiệu suất lọc.
+Lõi lọc được thiết kế chắc chắn, dễ dàng tháo lắp. Đầu tư ngay Combo 2 Lõi Lọc K195 để bảo vệ thiết bị lọc nước của bạn và duy trì chất lượng nước tốt nhất!</t>
+  </si>
+  <si>
+    <t>16381031412</t>
+  </si>
+  <si>
+    <t>Bộ Lọc Nước Cho Vòi Sen, Lavabo, Máy Giặt – Dễ Lắp Đặt, Lọc Sạch Bùn Cát K195</t>
+  </si>
+  <si>
+    <t>Bộ Lọc Nước Đầu Nguồn Vòi Hoa Sen,Bồn Rửa Chén,Lavabo,Máy Giặt Lọc Siêu Sạch Các Tạp Chất Dễ Dàng Lắp Đặt Không Ảnh Hưởng Đến Áp Lực Nước K195
+Ưu Điểm Lớn Nhất của sản phẩm là: 
+- Lọc Cặn Siêu Nhỏ (0.5 - 5micron) có khả năng lọc tất cả các tạp chất như bùn, cát mịn, giun, rong rêu, trứng côn trùng Và Không ảnh hưởng đến áp lực nước
+- Lọc nước sạch và trong
+- An toàn khi sử dụng với nước nóng
+- Dễ dàng lắp đặt
+- Thích hợp cho các loại vòi và vòi hoa sen (Ren kích thước tiêu chuẩn 21)
+- Lõi lọc bông PP có thể thay thế được. Thời gian dùng từ 1 - 3 tháng tùy thuộc vào tình trạng sạch dơ của nước.
+   Thông Tin Sản Phẩm
+  - Phân Loại 1 : 
+ - Tên Sản Phẩm : Bộ Lọc Nước Đầu Nguồn
+ - Chất Liệu : Nhựa PP Cao Cấp An Toàn
+ - Kích Thước : 15,9cm x 7,5 cm
+ - Bộ Sản Phẩm Gồm : Bộ Lọc Nước + Kèm Lõi Lọc
+ - Hướng Dẫn Sử Dụng : Lắp Đặt Phù hợp với dây sen, dây xịt, dây cấp nước, van khóa nước có ren 21mm (4 phân)
+ - Xuất Xứ : Trung Quốc
+ - Sản Phẩm Được Nhập Và Phân Phối Bởi Kho Gia Dụng Huy Vân
+ - .
+Phân Loại 2 : 
+ - Tên Sản Phẩm : Lõi Lọc Thay Thế
+ - Chất Liệu : Bông PP Cao Cấp 5 Micron Lọc Sạch Các Tạp Chất Siêu Nhỏ
+ - Lõi: màn lọc PP 0.5 - 5micron
+ - Kích Thước : 11,8cm x 4,7 cm
+ - Hướng Dẫn Sử Dụng : Lắp Đặt Thay Thế Lõi Lọc Cho Bộ Lọc Đầu Nguồn
+ - Xuất Xứ : Trung Quốc
+ ★ Lưu ý: 
+  - do chênh lệch ánh sáng và màn hình, màu sắc của sản phẩm có thể hơi khác so với hình ảnh.
+  - Vui Lòng Cho Phép Sai Số 1-2cm do đo lường thủ công
+ Dịch vụ tốt nhất:
+ ★ Cam Kết Sản Phẩm Và Chất Lượng Như Hình Và Video Shop Đăng,Tuyệt Đối Không Bán Hàng Kém Chất Lượng ảnh hưởng đến UY TÍN Của Shop
+ ★ Ship Hoả Tốc Trong Vòng 2H Kể Từ Khi Khách Đặt Hàng (Xác Nhận Đơn Đến 19-20H Hàng Ngày)
+ ★ Cam Kết Giao Đơn Hàng Cho Đơn Vị Vận Chuyển Trong Vòng 24H Kể Từ Khi Qúi Khách Đặt Hàng
+ ★ Hàng Hoá Luôn Có Sẵn Khách Đặt Được Là Còn Hàng ( Nếu Hết Hàng Shop Sẽ Gọi Điện Liên Hệ Khách Trước Khi Giao)
+ ★ Luôn Kiểm Tra Kỹ Hàng Hoá Trước Khi Giao Cho Khách.
+ ★ Bảo vệ khách hàng : Khi Nhận Được Sản Phẩm Bị Thiếu Hoặc Lỗi Do Phía Vận Chuyển Qúi Khách Vui Lòng Liên Hệ Lại Shop Để Shop xử lý Vấn Đề Ngay ạ
+ ★ Qúi Khách có thể thấy rằng ai đó bán với giá thấp hơn chúng tôi nhưng họ không thể đảm bảo chất lượng và dịch vụ như chúng tôi, cảm ơn bạn!
+#bolocvoisen #bolocvoihoasen #bolocsentam #bolocnuocvoisen #bolocnuocvoihoasen #bolocnuocsentam</t>
   </si>
   <si>
     <t>3124379936</t>
